--- a/artfynd/A 695-2023 artfynd.xlsx
+++ b/artfynd/A 695-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -885,6 +885,658 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128522320</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56573</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>206002</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Brunlångöra</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Plecotus auritus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Snäckstavik Box 6, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>656673</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6559629</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Alessandra Munari</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128522327</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56552</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Snäckstavik Box 6, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>656673</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6559629</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Alessandra Munari</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128522254</v>
+      </c>
+      <c r="B6" t="n">
+        <v>56566</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100092</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Nyctalus noctula</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Snäckstavik, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>656531</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6559428</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Alessandra Munari</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128522321</v>
+      </c>
+      <c r="B7" t="n">
+        <v>56571</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Snäckstavik Box 6, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>656673</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6559629</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Alessandra Munari</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128522326</v>
+      </c>
+      <c r="B8" t="n">
+        <v>56566</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100092</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Nyctalus noctula</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Snäckstavik Box 6, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>656673</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6559629</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Alessandra Munari</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128522324</v>
+      </c>
+      <c r="B9" t="n">
+        <v>56559</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>205992</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Myotis daubentonii</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Kuhl, 1817)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Snäckstavik Box 6, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>656673</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6559629</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Alessandra Munari</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 695-2023 artfynd.xlsx
+++ b/artfynd/A 695-2023 artfynd.xlsx
@@ -1209,10 +1209,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128522321</v>
+        <v>128522326</v>
       </c>
       <c r="B7" t="n">
-        <v>56571</v>
+        <v>56566</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1220,26 +1220,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1319,10 +1319,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128522326</v>
+        <v>128522321</v>
       </c>
       <c r="B8" t="n">
-        <v>56566</v>
+        <v>56571</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1330,26 +1330,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">

--- a/artfynd/A 695-2023 artfynd.xlsx
+++ b/artfynd/A 695-2023 artfynd.xlsx
@@ -1209,10 +1209,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128522326</v>
+        <v>128522321</v>
       </c>
       <c r="B7" t="n">
-        <v>56566</v>
+        <v>56571</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1220,26 +1220,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1319,10 +1319,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128522321</v>
+        <v>128522326</v>
       </c>
       <c r="B8" t="n">
-        <v>56571</v>
+        <v>56566</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1330,26 +1330,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">

--- a/artfynd/A 695-2023 artfynd.xlsx
+++ b/artfynd/A 695-2023 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>128522320</v>
       </c>
       <c r="B4" t="n">
-        <v>56573</v>
+        <v>56577</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>128522327</v>
       </c>
       <c r="B5" t="n">
-        <v>56552</v>
+        <v>56556</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>128522254</v>
       </c>
       <c r="B6" t="n">
-        <v>56566</v>
+        <v>56570</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1209,10 +1209,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128522321</v>
+        <v>128522326</v>
       </c>
       <c r="B7" t="n">
-        <v>56571</v>
+        <v>56570</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1220,26 +1220,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1319,10 +1319,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128522326</v>
+        <v>128522321</v>
       </c>
       <c r="B8" t="n">
-        <v>56566</v>
+        <v>56575</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1330,26 +1330,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1432,7 +1432,7 @@
         <v>128522324</v>
       </c>
       <c r="B9" t="n">
-        <v>56559</v>
+        <v>56563</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 695-2023 artfynd.xlsx
+++ b/artfynd/A 695-2023 artfynd.xlsx
@@ -1209,10 +1209,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128522326</v>
+        <v>128522321</v>
       </c>
       <c r="B7" t="n">
-        <v>56570</v>
+        <v>56575</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1220,26 +1220,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1319,10 +1319,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128522321</v>
+        <v>128522326</v>
       </c>
       <c r="B8" t="n">
-        <v>56575</v>
+        <v>56570</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1330,26 +1330,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">

--- a/artfynd/A 695-2023 artfynd.xlsx
+++ b/artfynd/A 695-2023 artfynd.xlsx
@@ -1209,10 +1209,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128522321</v>
+        <v>128522326</v>
       </c>
       <c r="B7" t="n">
-        <v>56575</v>
+        <v>56570</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1220,26 +1220,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1319,10 +1319,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128522326</v>
+        <v>128522321</v>
       </c>
       <c r="B8" t="n">
-        <v>56570</v>
+        <v>56575</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1330,26 +1330,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">

--- a/artfynd/A 695-2023 artfynd.xlsx
+++ b/artfynd/A 695-2023 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>128522320</v>
       </c>
       <c r="B4" t="n">
-        <v>56577</v>
+        <v>56604</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>128522327</v>
       </c>
       <c r="B5" t="n">
-        <v>56556</v>
+        <v>56583</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>128522254</v>
       </c>
       <c r="B6" t="n">
-        <v>56570</v>
+        <v>56597</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>128522326</v>
       </c>
       <c r="B7" t="n">
-        <v>56570</v>
+        <v>56597</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>128522321</v>
       </c>
       <c r="B8" t="n">
-        <v>56575</v>
+        <v>56602</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>128522324</v>
       </c>
       <c r="B9" t="n">
-        <v>56563</v>
+        <v>56590</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 695-2023 artfynd.xlsx
+++ b/artfynd/A 695-2023 artfynd.xlsx
@@ -1209,10 +1209,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128522326</v>
+        <v>128522321</v>
       </c>
       <c r="B7" t="n">
-        <v>56597</v>
+        <v>56602</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1220,26 +1220,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1319,10 +1319,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128522321</v>
+        <v>128522326</v>
       </c>
       <c r="B8" t="n">
-        <v>56602</v>
+        <v>56597</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1330,26 +1330,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">

--- a/artfynd/A 695-2023 artfynd.xlsx
+++ b/artfynd/A 695-2023 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>128522320</v>
       </c>
       <c r="B4" t="n">
-        <v>56604</v>
+        <v>56607</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>128522327</v>
       </c>
       <c r="B5" t="n">
-        <v>56583</v>
+        <v>56586</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>128522254</v>
       </c>
       <c r="B6" t="n">
-        <v>56597</v>
+        <v>56600</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1209,10 +1209,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128522321</v>
+        <v>128522326</v>
       </c>
       <c r="B7" t="n">
-        <v>56602</v>
+        <v>56600</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1220,26 +1220,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1319,10 +1319,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128522326</v>
+        <v>128522321</v>
       </c>
       <c r="B8" t="n">
-        <v>56597</v>
+        <v>56605</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1330,26 +1330,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1432,7 +1432,7 @@
         <v>128522324</v>
       </c>
       <c r="B9" t="n">
-        <v>56590</v>
+        <v>56593</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 695-2023 artfynd.xlsx
+++ b/artfynd/A 695-2023 artfynd.xlsx
@@ -1209,10 +1209,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128522326</v>
+        <v>128522321</v>
       </c>
       <c r="B7" t="n">
-        <v>56600</v>
+        <v>56605</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1220,26 +1220,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1319,10 +1319,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128522321</v>
+        <v>128522326</v>
       </c>
       <c r="B8" t="n">
-        <v>56605</v>
+        <v>56600</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1330,26 +1330,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">

--- a/artfynd/A 695-2023 artfynd.xlsx
+++ b/artfynd/A 695-2023 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>128522320</v>
       </c>
       <c r="B4" t="n">
-        <v>56607</v>
+        <v>56610</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>128522327</v>
       </c>
       <c r="B5" t="n">
-        <v>56586</v>
+        <v>56589</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>128522254</v>
       </c>
       <c r="B6" t="n">
-        <v>56600</v>
+        <v>56603</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1209,10 +1209,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128522321</v>
+        <v>128522326</v>
       </c>
       <c r="B7" t="n">
-        <v>56605</v>
+        <v>56603</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1220,26 +1220,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1319,10 +1319,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128522326</v>
+        <v>128522321</v>
       </c>
       <c r="B8" t="n">
-        <v>56600</v>
+        <v>56608</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1330,26 +1330,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1432,7 +1432,7 @@
         <v>128522324</v>
       </c>
       <c r="B9" t="n">
-        <v>56593</v>
+        <v>56596</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 695-2023 artfynd.xlsx
+++ b/artfynd/A 695-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1537,6 +1537,608 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>130881372</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57861</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Snäckstavik, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>656545</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6559736</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2009-01-25</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>08:04</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2009-01-25</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>08:04</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Stuart Fell</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Stuart Fell, Liam Martin</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>130882200</v>
+      </c>
+      <c r="B11" t="n">
+        <v>93100</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Snäckstavik, Srm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>656971</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6559356</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2010-01-25</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>08:19</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2010-01-25</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>08:19</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Stuart Fell</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Stuart Fell, Liam Martin</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>130881368</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57861</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Snäckstavik, Srm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>656968</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6559325</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2010-01-25</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>08:17</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2010-01-25</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>08:17</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Spår.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Stuart Fell</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Stuart Fell, Liam Martin</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>130882201</v>
+      </c>
+      <c r="B13" t="n">
+        <v>93062</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Snäckstavik, Srm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>656955</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6559350</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2010-01-25</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2010-01-25</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Stuart Fell</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Stuart Fell, Liam Martin</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>130881366</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57861</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Snäckstavik, Srm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>656781</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6559672</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2010-01-25</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2010-01-25</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Stuart Fell</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Stuart Fell</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 695-2023 artfynd.xlsx
+++ b/artfynd/A 695-2023 artfynd.xlsx
@@ -1904,42 +1904,47 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130882201</v>
+        <v>130881366</v>
       </c>
       <c r="B13" t="n">
-        <v>93062</v>
+        <v>57861</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1948,10 +1953,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>656955</v>
+        <v>656781</v>
       </c>
       <c r="R13" t="n">
-        <v>6559350</v>
+        <v>6559672</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1983,7 +1988,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1993,7 +1998,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2013,54 +2018,49 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Stuart Fell, Liam Martin</t>
+          <t>Stuart Fell</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130881366</v>
+        <v>130882201</v>
       </c>
       <c r="B14" t="n">
-        <v>57861</v>
+        <v>93062</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2069,10 +2069,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>656781</v>
+        <v>656955</v>
       </c>
       <c r="R14" t="n">
-        <v>6559672</v>
+        <v>6559350</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Stuart Fell</t>
+          <t>Stuart Fell, Liam Martin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 695-2023 artfynd.xlsx
+++ b/artfynd/A 695-2023 artfynd.xlsx
@@ -1904,47 +1904,42 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130881366</v>
+        <v>130882201</v>
       </c>
       <c r="B13" t="n">
-        <v>57861</v>
+        <v>93062</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1953,10 +1948,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>656781</v>
+        <v>656955</v>
       </c>
       <c r="R13" t="n">
-        <v>6559672</v>
+        <v>6559350</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1988,7 +1983,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1998,7 +1993,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2018,49 +2013,54 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Stuart Fell</t>
+          <t>Stuart Fell, Liam Martin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130882201</v>
+        <v>130881366</v>
       </c>
       <c r="B14" t="n">
-        <v>93062</v>
+        <v>57861</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2069,10 +2069,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>656955</v>
+        <v>656781</v>
       </c>
       <c r="R14" t="n">
-        <v>6559350</v>
+        <v>6559672</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Stuart Fell, Liam Martin</t>
+          <t>Stuart Fell</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 695-2023 artfynd.xlsx
+++ b/artfynd/A 695-2023 artfynd.xlsx
@@ -1665,7 +1665,7 @@
         <v>130882200</v>
       </c>
       <c r="B11" t="n">
-        <v>93100</v>
+        <v>93109</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>130882201</v>
       </c>
       <c r="B13" t="n">
-        <v>93062</v>
+        <v>93071</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 695-2023 artfynd.xlsx
+++ b/artfynd/A 695-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,42 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126646612</v>
+        <v>130882201</v>
       </c>
       <c r="B2" t="n">
-        <v>58027</v>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>656805</v>
+        <v>656955</v>
       </c>
       <c r="R2" t="n">
-        <v>6559582</v>
+        <v>6559350</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,12 +749,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2010-01-25</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>08:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2010-01-25</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>08:18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,22 +779,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Alessandra Munari</t>
+          <t>Stuart Fell</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Alessandra Munari</t>
+          <t>Stuart Fell, Liam Martin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126646616</v>
+        <v>130882200</v>
       </c>
       <c r="B3" t="n">
-        <v>58374</v>
+        <v>93235</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103055</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -814,9 +824,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -825,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>656563</v>
+        <v>656971</v>
       </c>
       <c r="R3" t="n">
-        <v>6559411</v>
+        <v>6559356</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,12 +865,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2010-01-25</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2010-01-25</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -875,39 +895,39 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Alessandra Munari</t>
+          <t>Stuart Fell</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alessandra Munari</t>
+          <t>Stuart Fell, Liam Martin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128522320</v>
+        <v>130881364</v>
       </c>
       <c r="B4" t="n">
-        <v>56610</v>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>206002</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -917,31 +937,32 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Snäckstavik Box 6, Srm</t>
+          <t>Snäckstavik, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>656673</v>
+        <v>656858</v>
       </c>
       <c r="R4" t="n">
-        <v>6559629</v>
+        <v>6559829</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -965,12 +986,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2010-01-25</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2010-01-25</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Flera Hackhål vid stambasen på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -985,73 +1021,74 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Alessandra Munari</t>
+          <t>Stuart Fell</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ellen Linder</t>
+          <t>Stuart Fell</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128522327</v>
+        <v>130881366</v>
       </c>
       <c r="B5" t="n">
-        <v>56589</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>205998</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Snäckstavik Box 6, Srm</t>
+          <t>Snäckstavik, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>656673</v>
+        <v>656781</v>
       </c>
       <c r="R5" t="n">
-        <v>6559629</v>
+        <v>6559672</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1075,12 +1112,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2010-01-25</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2010-01-25</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1095,22 +1142,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Alessandra Munari</t>
+          <t>Stuart Fell</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ellen Linder</t>
+          <t>Stuart Fell</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128522254</v>
+        <v>130881368</v>
       </c>
       <c r="B6" t="n">
-        <v>56603</v>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1118,39 +1165,48 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100092</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Snäckstavik, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>656531</v>
+        <v>656968</v>
       </c>
       <c r="R6" t="n">
-        <v>6559428</v>
+        <v>6559325</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1177,12 +1233,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2010-01-25</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2010-01-25</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>08:17</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Spår.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1197,22 +1268,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Alessandra Munari</t>
+          <t>Stuart Fell</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ellen Linder</t>
+          <t>Stuart Fell, Liam Martin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128522326</v>
+        <v>130881372</v>
       </c>
       <c r="B7" t="n">
-        <v>56603</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1220,50 +1291,53 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100092</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Snäckstavik Box 6, Srm</t>
+          <t>Snäckstavik, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>656673</v>
+        <v>656545</v>
       </c>
       <c r="R7" t="n">
-        <v>6559629</v>
+        <v>6559736</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1287,12 +1361,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2009-01-25</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>08:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2009-01-25</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>08:04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,22 +1391,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Alessandra Munari</t>
+          <t>Stuart Fell</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ellen Linder</t>
+          <t>Stuart Fell, Liam Martin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128522321</v>
+        <v>128522249</v>
       </c>
       <c r="B8" t="n">
-        <v>56608</v>
+        <v>56830</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1330,50 +1414,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Snäckstavik Box 6, Srm</t>
+          <t>Snäckstavik, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>656673</v>
+        <v>656730</v>
       </c>
       <c r="R8" t="n">
-        <v>6559629</v>
+        <v>6559499</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1397,12 +1473,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1429,10 +1505,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128522324</v>
+        <v>128522254</v>
       </c>
       <c r="B9" t="n">
-        <v>56596</v>
+        <v>56830</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1440,50 +1516,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Snäckstavik Box 6, Srm</t>
+          <t>Snäckstavik, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>656673</v>
+        <v>656531</v>
       </c>
       <c r="R9" t="n">
-        <v>6559629</v>
+        <v>6559428</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1507,12 +1575,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1539,64 +1607,61 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130881372</v>
+        <v>128522326</v>
       </c>
       <c r="B10" t="n">
-        <v>57881</v>
+        <v>56830</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100092</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Snäckstavik, Srm</t>
+          <t>Snäckstavik Box 6, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>656545</v>
+        <v>656673</v>
       </c>
       <c r="R10" t="n">
-        <v>6559736</v>
+        <v>6559629</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1620,22 +1685,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2009-01-25</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>08:04</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2009-01-25</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>08:04</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1650,44 +1705,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Stuart Fell</t>
+          <t>Alessandra Munari</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Stuart Fell, Liam Martin</t>
+          <t>Ellen Linder</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130882200</v>
+        <v>126646612</v>
       </c>
       <c r="B11" t="n">
-        <v>93135</v>
+        <v>58327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5966</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1695,9 +1750,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>mycel</t>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1706,10 +1761,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>656971</v>
+        <v>656805</v>
       </c>
       <c r="R11" t="n">
-        <v>6559356</v>
+        <v>6559582</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1736,22 +1791,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2010-01-25</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>08:19</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2010-01-25</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>08:19</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1766,22 +1811,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Stuart Fell</t>
+          <t>Alessandra Munari</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Stuart Fell, Liam Martin</t>
+          <t>Alessandra Munari</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130881368</v>
+        <v>126646592</v>
       </c>
       <c r="B12" t="n">
-        <v>57881</v>
+        <v>58676</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1789,21 +1834,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>103055</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1811,14 +1856,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1827,10 +1867,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>656968</v>
+        <v>656601</v>
       </c>
       <c r="R12" t="n">
-        <v>6559325</v>
+        <v>6559413</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1857,27 +1897,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2010-01-25</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>08:17</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2010-01-25</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>08:17</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Spår.</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1892,22 +1917,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Stuart Fell</t>
+          <t>Alessandra Munari</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Stuart Fell, Liam Martin</t>
+          <t>Alessandra Munari</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130881366</v>
+        <v>126646616</v>
       </c>
       <c r="B13" t="n">
-        <v>57881</v>
+        <v>58676</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1915,21 +1940,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>103055</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1937,14 +1962,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1953,10 +1973,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>656781</v>
+        <v>656563</v>
       </c>
       <c r="R13" t="n">
-        <v>6559672</v>
+        <v>6559411</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1983,22 +2003,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2010-01-25</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>08:48</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2010-01-25</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>08:48</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2013,22 +2023,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Stuart Fell</t>
+          <t>Alessandra Munari</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Stuart Fell</t>
+          <t>Alessandra Munari</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130882201</v>
+        <v>128522324</v>
       </c>
       <c r="B14" t="n">
-        <v>93097</v>
+        <v>56823</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2036,46 +2046,50 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>205992</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Snäckstavik, Srm</t>
+          <t>Snäckstavik Box 6, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>656955</v>
+        <v>656673</v>
       </c>
       <c r="R14" t="n">
-        <v>6559350</v>
+        <v>6559629</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2099,22 +2113,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2010-01-25</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>08:18</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2010-01-25</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>08:18</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2129,15 +2133,549 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Stuart Fell</t>
+          <t>Alessandra Munari</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Stuart Fell, Liam Martin</t>
+          <t>Ellen Linder</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128522250</v>
+      </c>
+      <c r="B15" t="n">
+        <v>56835</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Snäckstavik, Srm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>656621</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6559506</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Alessandra Munari</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128522321</v>
+      </c>
+      <c r="B16" t="n">
+        <v>56835</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Snäckstavik Box 6, Srm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>656673</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6559629</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Alessandra Munari</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128522255</v>
+      </c>
+      <c r="B17" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Snäckstavik, Srm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>656623</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6559502</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Alessandra Munari</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128522327</v>
+      </c>
+      <c r="B18" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Snäckstavik Box 6, Srm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>656673</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6559629</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Alessandra Munari</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128522320</v>
+      </c>
+      <c r="B19" t="n">
+        <v>56837</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>206002</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Brunlångöra</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Plecotus auritus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Snäckstavik Box 6, Srm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>656673</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6559629</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Alessandra Munari</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 695-2023 artfynd.xlsx
+++ b/artfynd/A 695-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130882201</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130882200</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1030,6 +1045,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130881364</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1151,6 +1171,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130881366</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1277,6 +1302,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130881368</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1400,6 +1430,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130881372</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1502,6 +1537,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128522249</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1604,6 +1644,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128522254</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1714,6 +1759,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128522326</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1820,6 +1870,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126646612</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1926,6 +1981,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126646592</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2032,6 +2092,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126646616</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2142,6 +2207,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128522324</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2244,6 +2314,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128522250</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2354,6 +2429,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128522321</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2456,6 +2536,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128522255</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2566,6 +2651,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128522327</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2676,8 +2766,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128522320</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>